--- a/data/trans_orig/P79A5_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P79A5_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20574</t>
+          <t>22178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28553</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,47%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11236</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22277</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25259</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16462</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>35838</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>44636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>18206</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>61709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
